--- a/AAII_Financials/Yearly/SYK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SYK_YR_FIN.xlsx
@@ -1251,13 +1251,13 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-207000</v>
+        <v>-86000</v>
       </c>
       <c r="E20" s="3">
-        <v>-215000</v>
+        <v>-76000</v>
       </c>
       <c r="F20" s="3">
-        <v>-148000</v>
+        <v>-73000</v>
       </c>
       <c r="G20" s="3">
         <v>-157000</v>
@@ -1302,13 +1302,13 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>6695000</v>
+        <v>6574000</v>
       </c>
       <c r="E21" s="3">
-        <v>5794000</v>
+        <v>5655000</v>
       </c>
       <c r="F21" s="3">
-        <v>4897000</v>
+        <v>4822000</v>
       </c>
       <c r="G21" s="3">
         <v>4337000</v>
@@ -1863,13 +1863,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>207000</v>
+        <v>86000</v>
       </c>
       <c r="E32" s="3">
-        <v>215000</v>
+        <v>76000</v>
       </c>
       <c r="F32" s="3">
-        <v>148000</v>
+        <v>73000</v>
       </c>
       <c r="G32" s="3">
         <v>157000</v>
